--- a/artfynd/A 47547-2022 artfynd.xlsx
+++ b/artfynd/A 47547-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47547-2022 artfynd.xlsx
+++ b/artfynd/A 47547-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>104495709</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>807898.5314661451</v>
+        <v>807898</v>
       </c>
       <c r="R2" t="n">
-        <v>7323477.097126363</v>
+        <v>7323477</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -748,19 +743,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104495684</v>
+        <v>104495710</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>807344.0360230567</v>
+        <v>807726</v>
       </c>
       <c r="R3" t="n">
-        <v>7322814.343579544</v>
+        <v>7323167</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -860,19 +840,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104495696</v>
+        <v>104495711</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>807717.3743653295</v>
+        <v>807878</v>
       </c>
       <c r="R4" t="n">
-        <v>7323169.089338527</v>
+        <v>7323370</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -972,19 +937,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104495702</v>
+        <v>104495712</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>807684.0542244116</v>
+        <v>807733</v>
       </c>
       <c r="R5" t="n">
-        <v>7323202.567505724</v>
+        <v>7323347</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1084,19 +1034,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104495711</v>
+        <v>104495714</v>
       </c>
       <c r="B6" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>807877.9718572196</v>
+        <v>807418</v>
       </c>
       <c r="R6" t="n">
-        <v>7323369.8126555</v>
+        <v>7322965</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1196,19 +1131,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104495710</v>
+        <v>104495719</v>
       </c>
       <c r="B7" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>807726.2448563953</v>
+        <v>807405</v>
       </c>
       <c r="R7" t="n">
-        <v>7323167.164655811</v>
+        <v>7322886</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1308,19 +1228,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,19 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104495704</v>
+        <v>104495702</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>807881.7733106051</v>
+        <v>807684</v>
       </c>
       <c r="R8" t="n">
-        <v>7323368.98808596</v>
+        <v>7323203</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1420,19 +1325,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104495692</v>
+        <v>104495703</v>
       </c>
       <c r="B9" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>807887.5911426984</v>
+        <v>807879</v>
       </c>
       <c r="R9" t="n">
-        <v>7323376.209835455</v>
+        <v>7323370</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1532,19 +1422,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104495690</v>
+        <v>104495704</v>
       </c>
       <c r="B10" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>807723.3908146648</v>
+        <v>807882</v>
       </c>
       <c r="R10" t="n">
-        <v>7323166.855936336</v>
+        <v>7323369</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1644,19 +1519,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104495688</v>
+        <v>104495705</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>807490.6382403884</v>
+        <v>807921</v>
       </c>
       <c r="R11" t="n">
-        <v>7322999.949789888</v>
+        <v>7323428</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1756,24 +1616,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104495687</v>
+        <v>104495706</v>
       </c>
       <c r="B12" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>807308.9559757514</v>
+        <v>807810</v>
       </c>
       <c r="R12" t="n">
-        <v>7322806.845898188</v>
+        <v>7323392</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1873,19 +1713,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104495714</v>
+        <v>104495700</v>
       </c>
       <c r="B13" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>807418.1101670831</v>
+        <v>807357</v>
       </c>
       <c r="R13" t="n">
-        <v>7322964.917083008</v>
+        <v>7322800</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1985,19 +1810,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104495719</v>
+        <v>104495701</v>
       </c>
       <c r="B14" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>807405.1803894993</v>
+        <v>807307</v>
       </c>
       <c r="R14" t="n">
-        <v>7322886.054562124</v>
+        <v>7322809</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2097,19 +1907,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104495705</v>
+        <v>104495684</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2152,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>807921.1200127401</v>
+        <v>807344</v>
       </c>
       <c r="R15" t="n">
-        <v>7323428.45511432</v>
+        <v>7322814</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2209,19 +2004,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104495691</v>
+        <v>104495687</v>
       </c>
       <c r="B16" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>807858.5680297299</v>
+        <v>807309</v>
       </c>
       <c r="R16" t="n">
-        <v>7323392.844704714</v>
+        <v>7322807</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2321,19 +2101,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104495698</v>
+        <v>104495696</v>
       </c>
       <c r="B17" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2400,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>807891.4917388663</v>
+        <v>807717</v>
       </c>
       <c r="R17" t="n">
-        <v>7323378.280035403</v>
+        <v>7323169</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2433,19 +2198,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104495689</v>
+        <v>104495697</v>
       </c>
       <c r="B18" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>807564.0127682078</v>
+        <v>807855</v>
       </c>
       <c r="R18" t="n">
-        <v>7323030.95539856</v>
+        <v>7323402</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2545,19 +2295,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,37 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104495700</v>
+        <v>104495690</v>
       </c>
       <c r="B19" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>807357.0815453544</v>
+        <v>807723</v>
       </c>
       <c r="R19" t="n">
-        <v>7322800.506373134</v>
+        <v>7323167</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2657,19 +2392,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,37 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104495706</v>
+        <v>104495691</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2736,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>807810.3837397699</v>
+        <v>807858</v>
       </c>
       <c r="R20" t="n">
-        <v>7323392.162287999</v>
+        <v>7323393</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2769,19 +2489,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2808,37 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104495701</v>
+        <v>104495692</v>
       </c>
       <c r="B21" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2848,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>807307.1049318814</v>
+        <v>807888</v>
       </c>
       <c r="R21" t="n">
-        <v>7322808.706290553</v>
+        <v>7323376</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2881,19 +2586,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2923,12 +2618,7 @@
         <v>104495718</v>
       </c>
       <c r="B22" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>807858.5680297299</v>
+        <v>807858</v>
       </c>
       <c r="R22" t="n">
-        <v>7323392.844704714</v>
+        <v>7323393</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2993,19 +2683,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3032,37 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104495703</v>
+        <v>104495698</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3072,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>807878.7872404684</v>
+        <v>807891</v>
       </c>
       <c r="R23" t="n">
-        <v>7323369.900906363</v>
+        <v>7323378</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3105,19 +2780,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3144,37 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104495697</v>
+        <v>104495693</v>
       </c>
       <c r="B24" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3184,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>807855.5599885463</v>
+        <v>807722</v>
       </c>
       <c r="R24" t="n">
-        <v>7323401.583139177</v>
+        <v>7323341</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3217,19 +2877,14 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3256,37 +2911,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104495694</v>
+        <v>104495688</v>
       </c>
       <c r="B25" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3296,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>807907.3902754429</v>
+        <v>807490</v>
       </c>
       <c r="R25" t="n">
-        <v>7323471.464215586</v>
+        <v>7323000</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3329,19 +2979,14 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3365,6 +3010,200 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>104495689</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Råtjärnarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>807564</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7323031</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-11-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-11-05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>104495694</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Råtjärnarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>807907</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7323471</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-11-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-11-05</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47547-2022 artfynd.xlsx
+++ b/artfynd/A 47547-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495709</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495710</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495711</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495712</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495714</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495719</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495702</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495703</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495704</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495705</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495706</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495700</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495701</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495684</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495687</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495696</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495697</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495690</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495691</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495692</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495718</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495698</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2908,6 +3023,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495693</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3010,6 +3130,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495688</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3107,6 +3232,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495689</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3204,8 +3334,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495694</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>